--- a/assets/PanglaoDB/cellsubtypes.xlsx
+++ b/assets/PanglaoDB/cellsubtypes.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="libxl" lastEdited="7" lowestEdited="7" rupBuild="4.6.0"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcai\Documents\GitHub\scGEAToolbox\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\claude_dev\scGEAToolbox_dev\assets\PanglaoDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41E9983-1D51-40EB-B3C3-97C97318751F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23183940-0774-4EC4-A46C-17A7A152147D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="472" uniqueCount="242">
   <si>
     <t>PositiveMarkers</t>
   </si>
@@ -54,9 +54,6 @@
     <t>M2</t>
   </si>
   <si>
-    <t>CD115,CD206,PPARG,ARG1,CD163,CD301,Dectin-1,PDL2,Fizz1</t>
-  </si>
-  <si>
     <t>CCR2,CSF1R,MARCO,PDL2,CD40,CCL2,CSF1,CD16,PDGFB</t>
   </si>
   <si>
@@ -192,9 +189,6 @@
     <t>Helper</t>
   </si>
   <si>
-    <t>IFNG,IL2,TBX21,DPP4,KLRD1,CXCR3,CCR1,CCR5,TNFSF11,HAVCR2,IL18R1,LTBR,TNF,LTA,GATA3,CSF2,IL4,IL5,IL6,IL10,IL13,CCR8,CXCR4,CCR3,CCR7,ICOS,PTGDR2,HAVCR1,IL1R2,IRF4,STAT6,IL17A,IL17F,IL21,IL22,RORA,RORC,CD38,KLRB1,AHR,CCR10,CD3D,CD4,CCR4,CCR6,IL9,CD2,CD28,CD5,IL1RL1,FOXP3,CD3G,TNFRSF4,CD40LG,IL17RB,HPGDS,NFATC2,NFKB1,NR3C1,PPARG</t>
-  </si>
-  <si>
     <t>Memory</t>
   </si>
   <si>
@@ -205,13 +199,565 @@
   </si>
   <si>
     <t>FOXP3,IKZF2,CD4,IL2RA,ENTPD1,SELL,NT5E,ITGAE,TNFRSF4,CTLA4,CCR4,LAG3,IZUMO1R,CNGB1,TNFRSF18,MAF,IL10,IL1R1,ITGB8,LRRC32,FOLR1</t>
+  </si>
+  <si>
+    <t>Central memory</t>
+  </si>
+  <si>
+    <t>Effector memory</t>
+  </si>
+  <si>
+    <t>Terminal effector</t>
+  </si>
+  <si>
+    <t>Tissue-resident memory</t>
+  </si>
+  <si>
+    <t>Th1</t>
+  </si>
+  <si>
+    <t>Th2</t>
+  </si>
+  <si>
+    <t>Th17</t>
+  </si>
+  <si>
+    <t>Exhausted</t>
+  </si>
+  <si>
+    <t>MAIT</t>
+  </si>
+  <si>
+    <t>Proliferating</t>
+  </si>
+  <si>
+    <t>CD3D,CD3E,CD4,CD40LG,IL7R,ICOS,CD28,LTB,MAL,TNFRSF4,CD2,ANXA1</t>
+  </si>
+  <si>
+    <t>CD3D,CD4,CCR7,SELL,IL7R,TCF7,LEF1,CD27,CD28,LTB,MAL,NOSIP,TRABD2A,S1PR1</t>
+  </si>
+  <si>
+    <t>CD3D,IL7R,GZMK,CCL5,CST7,GZMA,KLRG1,CD44,CXCR3,ANXA1,S100A4,AHNAK,CD8A</t>
+  </si>
+  <si>
+    <t>GZMB,GNLY,NKG7,FGFBP2,CX3CR1,KLRG1,TBX21,PRF1,FCGR3A,ADGRG1,S1PR5,ZEB2,KLRD1,SPON2,CD8A,CD8B</t>
+  </si>
+  <si>
+    <t>ITGAE,CD69,CXCR6,ITGA1,ZNF683,RUNX3,PDCD1,CD101,RGS1,DUSP6,NR4A1</t>
+  </si>
+  <si>
+    <t>TBX21,IFNG,CXCR3,IL12RB2,STAT4,CCR5,IL18R1,IL2,LTA,CSF2,CD4</t>
+  </si>
+  <si>
+    <t>GATA3,IL4,IL5,IL13,PTGDR2,CCR4,IL17RB,IL1RL1,STAT6,HPGDS,CCR8,IL9,CD4</t>
+  </si>
+  <si>
+    <t>RORC,RORA,IL17A,IL17F,CCR6,IL23R,KLRB1,IL22,AHR,IL21,CCL20,IL1R1,CD4</t>
+  </si>
+  <si>
+    <t>PDCD1,HAVCR2,LAG3,TIGIT,CTLA4,TOX,ENTPD1,LAYN,CXCL13,TNFRSF9,BATF,VSIR,CD38,EOMES</t>
+  </si>
+  <si>
+    <t>SLC4A10,KLRB1,ZBTB16,RORC,IL18R1,NCR3,CXCR6,DPP4,TRAV1-2,CCR6,GZMK,IL7R,CEBPD</t>
+  </si>
+  <si>
+    <t>MKI67,TOP2A,STMN1,TYMS,PCLAF,HMGB2,BIRC5,CENPF,UBE2C,CCNB1,NUSAP1,ASPM,RRM2,TUBB</t>
+  </si>
+  <si>
+    <t>PanglaoDB</t>
+  </si>
+  <si>
+    <t>Azimuth human PBMC reference (Hao et al., Cell 2021)</t>
+  </si>
+  <si>
+    <t>Azimuth human PBMC reference (Hao et al., Cell 2021); Sallusto et al., Nature 1999</t>
+  </si>
+  <si>
+    <t>Kumar et al., Cell Rep 2017; Szabo et al., Nat Commun 2019</t>
+  </si>
+  <si>
+    <t>Zhu &amp; Paul, Blood 2010</t>
+  </si>
+  <si>
+    <t>Wherry &amp; Kurachi, Nat Rev Immunol 2015; Zheng et al., Science 2021</t>
+  </si>
+  <si>
+    <t>Godfrey et al., Nat Immunol 2019</t>
+  </si>
+  <si>
+    <t>Whitfield et al., Mol Biol Cell 2002</t>
+  </si>
+  <si>
+    <t>Generic CD4+ helper; the Th1/Th2/Th17 rows carry the lineage-specific programs that used to be pooled here.</t>
+  </si>
+  <si>
+    <t>TCM</t>
+  </si>
+  <si>
+    <t>TEM</t>
+  </si>
+  <si>
+    <t>TEMRA; CD45RA-re-expressing terminally differentiated effector</t>
+  </si>
+  <si>
+    <t>TRM</t>
+  </si>
+  <si>
+    <t>Mucosal-associated invariant T</t>
+  </si>
+  <si>
+    <t>Cycling T cells, so a dividing cluster is not labeled by lineage markers alone</t>
+  </si>
+  <si>
+    <t>CD115,CD206,PPARG,ARG1,CD163,CD301,CLEC7A,PDL2,RETNLB</t>
+  </si>
+  <si>
+    <t>B cells</t>
+  </si>
+  <si>
+    <t>NK cells</t>
+  </si>
+  <si>
+    <t>Monocytes</t>
+  </si>
+  <si>
+    <t>Dendritic cells</t>
+  </si>
+  <si>
+    <t>Neutrophils</t>
+  </si>
+  <si>
+    <t>Fibroblasts</t>
+  </si>
+  <si>
+    <t>Endothelial cells</t>
+  </si>
+  <si>
+    <t>Epithelial cells</t>
+  </si>
+  <si>
+    <t>Astrocytes</t>
+  </si>
+  <si>
+    <t>Microglia</t>
+  </si>
+  <si>
+    <t>Oligodendrocytes</t>
+  </si>
+  <si>
+    <t>Tissue-resident</t>
+  </si>
+  <si>
+    <t>Lipid-associated</t>
+  </si>
+  <si>
+    <t>Monocyte-derived</t>
+  </si>
+  <si>
+    <t>Germinal center</t>
+  </si>
+  <si>
+    <t>Atypical memory</t>
+  </si>
+  <si>
+    <t>Plasmablast</t>
+  </si>
+  <si>
+    <t>Plasma cell</t>
+  </si>
+  <si>
+    <t>CD56 bright</t>
+  </si>
+  <si>
+    <t>CD56 dim</t>
+  </si>
+  <si>
+    <t>Adaptive</t>
+  </si>
+  <si>
+    <t>Classical</t>
+  </si>
+  <si>
+    <t>Non-classical</t>
+  </si>
+  <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
+    <t>cDC1</t>
+  </si>
+  <si>
+    <t>cDC2</t>
+  </si>
+  <si>
+    <t>Plasmacytoid</t>
+  </si>
+  <si>
+    <t>Langerhans</t>
+  </si>
+  <si>
+    <t>Mature migratory</t>
+  </si>
+  <si>
+    <t>Mature</t>
+  </si>
+  <si>
+    <t>Activated</t>
+  </si>
+  <si>
+    <t>Myofibroblastic</t>
+  </si>
+  <si>
+    <t>Inflammatory</t>
+  </si>
+  <si>
+    <t>Antigen-presenting</t>
+  </si>
+  <si>
+    <t>Universal</t>
+  </si>
+  <si>
+    <t>Arterial</t>
+  </si>
+  <si>
+    <t>Venous</t>
+  </si>
+  <si>
+    <t>Capillary</t>
+  </si>
+  <si>
+    <t>Lymphatic</t>
+  </si>
+  <si>
+    <t>Tip cell</t>
+  </si>
+  <si>
+    <t>Basal</t>
+  </si>
+  <si>
+    <t>Luminal secretory</t>
+  </si>
+  <si>
+    <t>Ciliated</t>
+  </si>
+  <si>
+    <t>Goblet</t>
+  </si>
+  <si>
+    <t>Protoplasmic</t>
+  </si>
+  <si>
+    <t>Fibrous</t>
+  </si>
+  <si>
+    <t>Reactive</t>
+  </si>
+  <si>
+    <t>Homeostatic</t>
+  </si>
+  <si>
+    <t>Interferon-response</t>
+  </si>
+  <si>
+    <t>Precursor</t>
+  </si>
+  <si>
+    <t>Newly formed</t>
+  </si>
+  <si>
+    <t>Myelinating</t>
+  </si>
+  <si>
+    <t>IL1A,IL1B,IL6,NOS2,TLR2,TLR4,CD80,CD86</t>
+  </si>
+  <si>
+    <t>CSF1R,MRC1,PPARG,ARG1,CD163,CLEC10A,CLEC7A,PDCD1LG2,RETNLB</t>
+  </si>
+  <si>
+    <t>CCR2,CSF1R,MARCO,PDCD1LG2,CD40,CCL2,CSF1,FCGR3A,PDGFB</t>
+  </si>
+  <si>
+    <t>LYVE1,FOLR2,MRC1,CD163,SELENOP,F13A1,STAB1,CD209</t>
+  </si>
+  <si>
+    <t>TREM2,APOE,SPP1,GPNMB,CD9,LPL,FABP5,CTSD</t>
+  </si>
+  <si>
+    <t>FCN1,S100A8,S100A9,VCAN,IL1B,CXCL8,CD14,SELL</t>
+  </si>
+  <si>
+    <t>MKI67,TOP2A,STMN1,TYROBP,C1QA,CD68</t>
+  </si>
+  <si>
+    <t>HIVEP3,PLEKHA5,IGF2BP3,ARHGAP26,TTBK2,ASTN1,CACNA1E,TUB,FILIP1,GCNT2,VEZT,RET,AHDC1,MAP6,RGMB,FBXO7,PPP2R5B,SNX21,FSTL5,LIX1,RGS3,CYTH3,TSHZ1,STXBP5,ATF5,DMKN,CACNA1B,PIK3CA,ZDHHC2,MYL1,EML5,MFSD6,SCN7A,ARHGEF28,HAND2,VSTM2L,TAFA5,FAM19A5,EFNA5,HOXB4,TLX2,GOLGA7B,SLC18A3,TOX,CELF6,GPR22,PLCE1,CYB561,GFRA2,FLOT2,SLC7A14,JPH3,CASZ1,TAC1,SCN3A,CHRNA3,PARVA,SLC10A4,TM4SF4,TAFA1,FAM19A1,SLC5A7,PHOX2B,PIRT,HOXB5,HOXA5,GAL,CARTPT,NMU,VIP,CCK</t>
+  </si>
+  <si>
+    <t>CALB1,CCK,CHAT,VSX2,EN1,ETV1,EVX1,GAD1,ISL1,LHX1,LHX5,LHX3,LHX6,GRM1,NPY,OPRM1,GRIN2D,NOS1,PVALB,PAX2,SST,TACR1,VIP,CRHR1,PACSIN1,SYN1,FGF12,NXPH1,SYT7,PTPRO,DLGAP1,GNG4,HAP1,SHISA8,PCBP3,ABAT,PCP4L1,GAL,TH,SYNPR,TRH,ADCY8,CCN2,CTGF,EML5,TMEM132D,BACE1,CACNG2,ISCA1,LPGAT1,NAT14,SLC12A5,DEPTOR,SLC22A15,PDE4A,CACNA1I,FRYL,SURF1,TRIM9,KCNC1,RAB3B,CDK17,RGS17,ABCC5,RAB26,VLDLR,CACNG7,INAFM1,BRINP1,PIANP,CPLX1,SHISA6,DHRS3,GRIA4,NRSN2,CDHR1,ABR,NRN1,HIVEP2,NXPH4,CDH4,CHST1,SHISA9,EOMES,NMB,LY6G6E,CALN1,CASK,CACNA1E,FAM81A,CAMKV,ARHGAP21,DDN,SV2B,FRRS1L,ACSL4,CAMK4,NPTXR,LINGO1,HPCAL4,LMO3,LYPD1,CHN1,NRGN,SLC17A7,CAMK2A,PRKCB,NCALD,RAB15,FBXW11,ADCY1,FBXO11,IGSF21,SRGAP3,NTNG1,MAGEE1,SCAMP1,PSD3,RORA,DCAF7,VGF,EID2,RGMA,SCRT1,POU2F2,NBEA,SRGAP1,FCHSD2,SLC16A1,SLC36A1,ATG12,SLC17A6,AGAP1,ZDHHC22,ACBD5,AQP4,TMEM163,ZDHHC17,ZIC4,NEFM,L1CAM,IDS,DNM3,DNAJC6,ADGRA1,DZANK1,SCN2B,HSPA12A,SYT13,RAMP3,LYNX1,KCNA2,OXR1,DISP2,PCSK2,SHOX2,SCN8A,AAK1,GABRA4,NRIP3,HLF,PRKCD,PTPN3,KCNC2,CDKL5,CCDC136,KCNMA1,SPOCK3,PTPN4,PDP1,RGS7BP,PLCB4,GABBR2,ELMO1,ADARB1,ILDR2,AKAP8L,SPTY2D1,PCF11,PARM1,PITX2,PITX1,CLDN9,TCEAL3,KCNK9,TSHB,RORB,GATA2,TIMELESS,CXCL14,APOC3,CGA,ADORA2A,RPRML,CACNB1,KCNQ5,PRKCG,GABRA5,PAX6,PNOC,HTR3A,RELN,CALB2,PDE1A,ADGRL2,KCNIP2,RGS10,CCN3,NOV,CPNE5,SLC5A7,CRH,GDA,SEMA3E,DLX1,DLX2,DLX5,ARX,NDNF</t>
+  </si>
+  <si>
+    <t>GNLY,PTGDS,GZMB,S100B,FGFBP2,NKG7,PRF1,KLRF1,HOPX,CST7,KLRD1,CTSW,SPON2,IFITM1,GZMA,CD247,CLIC3,CD7,ADGRG1,CCL5,TRDC,STMN1,HMGB2,TYMS,MKI67,UBE2C,TUBA1B,ASPM,CENPA,TOP2A,PCNA,AURKB,BIRC5,NUSAP1,TROAP,TUBB,H2AX,H2AFX,CENPF,CCNB1,H2AZ1,H2AFZ,TRGV2,TRGV10,TRGV11,TRGV1,TRGV3,TRGV4,TRGV5,TRGV8,TRGV9,TRGJ1,TRGJ2,TRGJP1,TRGJP2,TRGJP,TRGC1,TRGC2,TRDD1,TRDD2,TRDD3,TRDJ1,TRDJ2,TRDJ3,TRDJ4,TRDV1,TRDV2,TRDV3</t>
+  </si>
+  <si>
+    <t>SELL,CCR7,CD4,CCR5,CD69,ITGB5,BCL2,GRAP2,TBC1D10C,CYTIP,KPNA4,CD247,EPSTI1,APBB1IP,CD27,RHOH,GIMAP1,ACP5,IKZF1,SP100,DGKA,IL7R,ITGB7,NKG7,CD28,BIN2,RAPGEF6,ARHGEF1,S100A9,ARHGAP15,CD3E,SKAP1,GIMAP4,CD2,PTPRC,LAT,TCF7,LEF1,SEPTIN1,SEPT1,ARHGAP45,SATB1,PTPRCAP,S100A8,LTB,LCK,TRAC,CD3G,CD3D,TRBC2,CD7,CXCR6,ICOS,CCR6,ITGAE,ENPP1</t>
+  </si>
+  <si>
+    <t>MS4A1,CD79A,CD79B,IGHD,IGHM,TCL1A,FCER2,CR2,IL4R,BACH2,SELL,CD37</t>
+  </si>
+  <si>
+    <t>MS4A1,CD27,TNFRSF13B,IGHG1,IGHA1,AIM2,CD79A,CD24,TXNIP,COCH</t>
+  </si>
+  <si>
+    <t>BCL6,AICDA,RGS13,MEF2B,S1PR2,GCSAM,LMO2,CXCR4,CD38,MKI67</t>
+  </si>
+  <si>
+    <t>ITGAX,TBX21,FCRL5,FGR,ZEB2,TNFRSF13B,MS4A1,CD19,SOX5</t>
+  </si>
+  <si>
+    <t>MZB1,XBP1,PRDM1,JCHAIN,TNFRSF17,IRF4,CD38,MKI67,TYMS</t>
+  </si>
+  <si>
+    <t>SDC1,MZB1,XBP1,PRDM1,JCHAIN,DERL3,TNFRSF17,IGHG1,SSR4,FKBP11,CD38</t>
+  </si>
+  <si>
+    <t>NCAM1,XCL1,XCL2,SELL,GZMK,IL7R,KLRC1,TCF7,GPR183,CD44</t>
+  </si>
+  <si>
+    <t>FCGR3A,GZMB,PRF1,NKG7,GNLY,FGFBP2,SPON2,KLRD1,CX3CR1,S1PR5,ZEB2</t>
+  </si>
+  <si>
+    <t>KLRC2,GZMH,IL32,CD52,LAG3,PRF1,FCGR3A,ZEB2,CD3E</t>
+  </si>
+  <si>
+    <t>MKI67,TOP2A,STMN1,TYMS,PCLAF,NKG7,GNLY</t>
+  </si>
+  <si>
+    <t>CD14,LYZ,S100A8,S100A9,S100A12,VCAN,FCN1,SELL,CSF3R,MNDA</t>
+  </si>
+  <si>
+    <t>FCGR3A,MS4A7,CDKN1C,LST1,LILRB2,CSF1R,TCF7L2,RHOC,HES4</t>
+  </si>
+  <si>
+    <t>CD14,FCGR3A,HLA-DRA,HLA-DRB1,CD74,MNDA,VCAN,CTSS,CX3CR1</t>
+  </si>
+  <si>
+    <t>CLEC9A,XCR1,BATF3,IRF8,CADM1,IDO1,WDFY4,DNASE1L3</t>
+  </si>
+  <si>
+    <t>CD1C,FCER1A,CLEC10A,IRF4,HLA-DQA1,CD1D,ITGAX,SIRPA</t>
+  </si>
+  <si>
+    <t>LILRA4,CLEC4C,IRF7,GZMB,JCHAIN,TCF4,IL3RA,SERPINF1,PLD4</t>
+  </si>
+  <si>
+    <t>CD207,CD1A,EPCAM,CD1C,ITGAX,S100B</t>
+  </si>
+  <si>
+    <t>CCR7,LAMP3,FSCN1,CCL19,CCL22,IL7R,MARCKSL1,IDO1,BIRC3</t>
+  </si>
+  <si>
+    <t>FCGR3B,CSF3R,CXCR2,S100A8,S100A9,IFITM2,BASP1,SRGN,SELL</t>
+  </si>
+  <si>
+    <t>MPO,ELANE,DEFA3,DEFA4,CAMP,LTF,LCN2,CEBPE,PRTN3</t>
+  </si>
+  <si>
+    <t>CXCR4,ITGAM,ICAM1,CD83,IL1B,CXCL8,NFKBIA,TNFAIP3</t>
+  </si>
+  <si>
+    <t>ACTA2,TAGLN,MYL9,POSTN,COL1A1,TPM2,CTHRC1,FN1,THBS2</t>
+  </si>
+  <si>
+    <t>CXCL12,CXCL14,C3,C7,PDGFRA,IL6,CFD,APOD,PLA2G2A</t>
+  </si>
+  <si>
+    <t>CD74,HLA-DRA,HLA-DRB1,HLA-DPA1,SLPI,CLU,SAA1</t>
+  </si>
+  <si>
+    <t>PI16,DPT,SEMA3C,CD34,MFAP5,IGFBP6,SCARA5,PCOLCE2</t>
+  </si>
+  <si>
+    <t>GJA5,HEY1,SEMA3G,EFNB2,DKK2,CXCL12,SOX17,NOTCH4</t>
+  </si>
+  <si>
+    <t>ACKR1,NR2F2,VWF,SELP,PLVAP,VCAM1,CPE</t>
+  </si>
+  <si>
+    <t>CA4,RGCC,CD36,FCN3,AQP1,SGK1,BTNL9</t>
+  </si>
+  <si>
+    <t>PROX1,PDPN,LYVE1,CCL21,FLT4,MMRN1,TFF3</t>
+  </si>
+  <si>
+    <t>ESM1,ANGPT2,APLN,CXCR4,DLL4,KDR,NID2,PGF</t>
+  </si>
+  <si>
+    <t>KRT5,KRT14,TP63,KRT15,ITGA6,DST,COL17A1</t>
+  </si>
+  <si>
+    <t>KRT8,KRT18,KRT19,ELF3,MUC1,CLDN4,EPCAM</t>
+  </si>
+  <si>
+    <t>FOXJ1,TPPP3,PIFO,CAPS,DNAI1,TEKT1,RSPH1</t>
+  </si>
+  <si>
+    <t>MUC5AC,MUC5B,TFF3,SPDEF,AGR2,CLCA1,FCGBP</t>
+  </si>
+  <si>
+    <t>SLC1A2,SLC1A3,GJA1,AQP4,MFGE8,GPC5,ATP1A2</t>
+  </si>
+  <si>
+    <t>GFAP,CD44,TNC,AQP4,ID3,CRYAB,HOPX</t>
+  </si>
+  <si>
+    <t>GFAP,VIM,SERPINA3,C3,CHI3L1,CD44,OSMR,TIMP1</t>
+  </si>
+  <si>
+    <t>P2RY12,TMEM119,CX3CR1,CSF1R,SALL1,SELPLG,MEF2C,OLFML3</t>
+  </si>
+  <si>
+    <t>APOE,TREM2,TYROBP,CD9,ITGAX,SPP1,LPL,CST7,CTSD,AXL,GPNMB</t>
+  </si>
+  <si>
+    <t>IFIT1,IFIT3,ISG15,IFI44L,MX1,OASL,STAT1,IRF7</t>
+  </si>
+  <si>
+    <t>MKI67,TOP2A,STMN1,PCLAF,TYROBP,C1QB</t>
+  </si>
+  <si>
+    <t>PDGFRA,CSPG4,SOX10,OLIG1,OLIG2,LHFPL3,PTPRZ1</t>
+  </si>
+  <si>
+    <t>BCAS1,GPR17,ITPR2,SIRT2,TCF7L2,ENPP6,FYN</t>
+  </si>
+  <si>
+    <t>MBP,PLP1,MOG,MAG,MOBP,CNP,CLDN11,ERMN</t>
+  </si>
+  <si>
+    <t>Dick et al., Sci Immunol 2022</t>
+  </si>
+  <si>
+    <t>Jaitin et al., Cell 2019</t>
+  </si>
+  <si>
+    <t>Zilionis et al., Immunity 2019</t>
+  </si>
+  <si>
+    <t>Milpied et al., Nat Immunol 2018</t>
+  </si>
+  <si>
+    <t>Holla et al., Sci Adv 2021</t>
+  </si>
+  <si>
+    <t>Schlums et al., Immunity 2015</t>
+  </si>
+  <si>
+    <t>Villani et al., Science 2017</t>
+  </si>
+  <si>
+    <t>Deckers et al., Front Immunol 2018</t>
+  </si>
+  <si>
+    <t>Maier et al., Nature 2020</t>
+  </si>
+  <si>
+    <t>Xie et al., Nat Immunol 2020</t>
+  </si>
+  <si>
+    <t>Elyada et al., Cancer Discov 2019</t>
+  </si>
+  <si>
+    <t>Buechler et al., Nature 2021</t>
+  </si>
+  <si>
+    <t>Kalucka et al., Cell 2020</t>
+  </si>
+  <si>
+    <t>Human Cell Landscape (Han et al., Nature 2020)</t>
+  </si>
+  <si>
+    <t>Travaglini et al., Nature 2020</t>
+  </si>
+  <si>
+    <t>Bayraktar et al., Nat Neurosci 2020</t>
+  </si>
+  <si>
+    <t>Liddelow et al., Nature 2017</t>
+  </si>
+  <si>
+    <t>Keren-Shaul et al., Cell 2017</t>
+  </si>
+  <si>
+    <t>Sala Frigerio et al., Cell Rep 2019</t>
+  </si>
+  <si>
+    <t>Marques et al., Science 2016</t>
+  </si>
+  <si>
+    <t>LAM</t>
+  </si>
+  <si>
+    <t>Also called age-associated or double-negative B cells</t>
+  </si>
+  <si>
+    <t>CD56bright CD16dim, cytokine-producing</t>
+  </si>
+  <si>
+    <t>CD56dim CD16bright, cytotoxic</t>
+  </si>
+  <si>
+    <t>Memory-like, expanded in CMV carriers</t>
+  </si>
+  <si>
+    <t>CD14++ CD16-</t>
+  </si>
+  <si>
+    <t>CD14+ CD16++</t>
+  </si>
+  <si>
+    <t>CD14++ CD16+</t>
+  </si>
+  <si>
+    <t>pDC</t>
+  </si>
+  <si>
+    <t>LAMP3+ mregDC</t>
+  </si>
+  <si>
+    <t>Band and promyelocyte stages</t>
+  </si>
+  <si>
+    <t>myCAF</t>
+  </si>
+  <si>
+    <t>iCAF</t>
+  </si>
+  <si>
+    <t>apCAF</t>
+  </si>
+  <si>
+    <t>PI16+ adventitial/universal fibroblast</t>
+  </si>
+  <si>
+    <t>Angiogenic sprout</t>
+  </si>
+  <si>
+    <t>Grey matter</t>
+  </si>
+  <si>
+    <t>White matter</t>
+  </si>
+  <si>
+    <t>Disease-associated microglia (DAM)</t>
+  </si>
+  <si>
+    <t>OPC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,30 +773,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
@@ -276,7 +798,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -284,21 +806,18 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -319,7 +838,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -436,7 +955,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -460,9 +979,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -486,7 +1005,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -521,7 +1040,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -539,7 +1058,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -564,7 +1083,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -580,322 +1099,1373 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F84"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.08984375" customWidth="1"/>
-    <col min="2" max="2" width="30.453125" customWidth="1"/>
-    <col min="3" max="3" width="48.54296875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="27.6328125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="28.6328125" customWidth="1"/>
-    <col min="6" max="6" width="18.453125" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="true"/>
+    <col min="2" max="2" width="22.7109375" customWidth="true"/>
+    <col min="3" max="3" width="1367.140625" style="1" customWidth="true"/>
+    <col min="4" max="4" width="16.28515625" style="2" customWidth="true"/>
+    <col min="5" max="5" width="73.28515625" customWidth="true"/>
+    <col min="6" max="6" width="97.28515625" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="0" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="0"/>
+      <c r="F2" s="0"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="0"/>
+      <c r="F4" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="F5" s="0"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="F7" s="0"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="0"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B9" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="0"/>
+      <c r="F9" s="0"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="7"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B10" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="0"/>
+      <c r="F10" s="0"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="7"/>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B11" s="0" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D11" s="2"/>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="0" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="C12" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="0" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D13" s="2"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="0"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D14" s="2"/>
+      <c r="E14" s="0"/>
+      <c r="F14" s="0"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="0" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D15" s="2"/>
+      <c r="E15" s="0"/>
+      <c r="F15" s="0"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="0" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D16" s="2"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="0" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="C17" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="0" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C18" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D18" s="2"/>
+      <c r="E18" s="0"/>
+      <c r="F18" s="0"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="0" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D19" s="2"/>
+      <c r="E19" s="0"/>
+      <c r="F19" s="0"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="0" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D20" s="2"/>
+      <c r="E20" s="0"/>
+      <c r="F20" s="0"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="0" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D21" s="2"/>
+      <c r="E21" s="0"/>
+      <c r="F21" s="0"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="0" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D22" s="2"/>
+      <c r="E22" s="0"/>
+      <c r="F22" s="0"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="B23" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="B19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="C23" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="0"/>
+      <c r="F23" s="0"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="0" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D24" s="2"/>
+      <c r="E24" s="0"/>
+      <c r="F24" s="0"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="0" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D25" s="2"/>
+      <c r="E25" s="0"/>
+      <c r="F25" s="0"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="0" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C26" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D26" s="2"/>
+      <c r="E26" s="0"/>
+      <c r="F26" s="0"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="0" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D27" s="2"/>
+      <c r="E27" s="0"/>
+      <c r="F27" s="0"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="0" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="0" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C29" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="0"/>
+      <c r="F29" s="0"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="D30" s="2"/>
+      <c r="E30" s="0"/>
+      <c r="F30" s="0"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="0" t="s">
         <v>59</v>
       </c>
+      <c r="C32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="F34" s="0" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="F35" s="0"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="F36" s="0"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="2"/>
+      <c r="E37" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="F37" s="0"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="2"/>
+      <c r="E38" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="F38" s="0"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="F40" s="0" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F41" s="0"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F42" s="0"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="F43" s="0"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="F44" s="0" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="E45" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F45" s="0"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F46" s="0"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="F49" s="0" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" s="2"/>
+      <c r="E50" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="F50" s="0"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D51" s="2"/>
+      <c r="E51" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F51" s="0" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D52" s="2"/>
+      <c r="E52" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F52" s="0" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D53" s="2"/>
+      <c r="E53" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F53" s="0" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D54" s="2"/>
+      <c r="E54" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="F54" s="0"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D55" s="2"/>
+      <c r="E55" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="F55" s="0"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D56" s="2"/>
+      <c r="E56" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="F56" s="0" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57" s="2"/>
+      <c r="E57" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="F57" s="0"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="F58" s="0" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D59" s="2"/>
+      <c r="E59" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F59" s="0"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D60" s="2"/>
+      <c r="E60" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F60" s="0" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D61" s="2"/>
+      <c r="E61" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="F61" s="0"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D62" s="2"/>
+      <c r="E62" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="F62" s="0" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D63" s="2"/>
+      <c r="E63" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="F63" s="0" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D64" s="2"/>
+      <c r="E64" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="F64" s="0" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D65" s="2"/>
+      <c r="E65" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="F65" s="0" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D66" s="2"/>
+      <c r="E66" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="F66" s="0"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D67" s="2"/>
+      <c r="E67" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="F67" s="0"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D68" s="2"/>
+      <c r="E68" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="F68" s="0"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D69" s="2"/>
+      <c r="E69" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="F69" s="0"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D70" s="2"/>
+      <c r="E70" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="F70" s="0" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D71" s="2"/>
+      <c r="E71" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="F71" s="0"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D72" s="2"/>
+      <c r="E72" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="F72" s="0"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D73" s="2"/>
+      <c r="E73" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="F73" s="0"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D74" s="2"/>
+      <c r="E74" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="F74" s="0"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D75" s="2"/>
+      <c r="E75" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="F75" s="0" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D76" s="2"/>
+      <c r="E76" s="0" t="s">
+        <v>217</v>
+      </c>
+      <c r="F76" s="0" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D77" s="2"/>
+      <c r="E77" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="F77" s="0"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D78" s="2"/>
+      <c r="E78" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="F78" s="0"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D79" s="2"/>
+      <c r="E79" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="F79" s="0" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D80" s="2"/>
+      <c r="E80" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="F80" s="0"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D81" s="2"/>
+      <c r="E81" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="F81" s="0"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D82" s="2"/>
+      <c r="E82" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="F82" s="0" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D83" s="2"/>
+      <c r="E83" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="F83" s="0"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D84" s="2"/>
+      <c r="E84" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="F84" s="0"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
